--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ILLINOIS_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/ILLINOIS_2012.xlsx
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C125">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C213">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C800">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C934">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C986">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C987">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C994">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1417">
@@ -26574,7 +26574,7 @@
       </c>
       <c r="B1457" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1457">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1610">
